--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_385_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_385_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>26</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>55:46</t>
+          <t>25:46</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>67:26</t>
+          <t>27:26</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>55:34</t>
+          <t>25:35</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,22 +1843,22 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>26:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>57:33</t>
+          <t>27:34</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2903,7 +2903,7 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>28:56</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>35:51</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>27:30</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3827,16 +3827,16 @@
         <v>102</v>
       </c>
       <c r="T30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -4292,16 +4292,16 @@
         <v>26</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>8</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>60:55</t>
+          <t>30:55</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>8</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>61:56</t>
+          <t>31:57</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
         <v>20</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>56:07</t>
+          <t>26:07</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,17 +4800,17 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>01:13</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5272,16 +5272,16 @@
         <v>8</v>
       </c>
       <c r="T40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>4</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>49:34</t>
+          <t>29:35</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>26:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5860,10 +5860,10 @@
         <v>8</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>46:27</t>
+          <t>26:28</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,22 +6172,22 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>34:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -6784,16 +6784,16 @@
         <v>89</v>
       </c>
       <c r="T48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X48" t="n">
         <v>35</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_385_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_385_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>26</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>18</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1727,16 +1727,16 @@
         <v>11</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>102</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -4292,16 +4292,16 @@
         <v>26</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>8</v>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X36" t="n">
         <v>8</v>
@@ -4684,7 +4684,7 @@
         <v>20</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5272,16 +5272,16 @@
         <v>8</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>4</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -5860,10 +5860,10 @@
         <v>8</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>89</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X48" t="n">
         <v>35</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_385_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_385_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>11</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>88.00</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="O3" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -851,20 +851,20 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>76.19</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Y30" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,10 +4304,10 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4500,14 +4500,14 @@
         <v>3</v>
       </c>
       <c r="X36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4533,25 +4533,25 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5480,14 +5480,14 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>5</v>
       </c>
       <c r="X48" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="Y48" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
